--- a/attachments/DSJ_AE_Platforms_and_Sharing_Economy.xlsx
+++ b/attachments/DSJ_AE_Platforms_and_Sharing_Economy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liangfeiqiu\Dropbox\UF\Review\DSJ EIC\DSJ EIC\DSJ board\Finalized\DSJ AEs and ERBs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E248F0B5-91E0-4E08-B369-886FAD7B06AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1908158B-DD0A-4CEA-8852-4E2E3D2F0B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="281">
   <si>
     <t>Last Name</t>
   </si>
@@ -862,6 +862,18 @@
   </si>
   <si>
     <t>First Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hong </t>
+  </si>
+  <si>
+    <t>Zheng</t>
+  </si>
+  <si>
+    <t>zhenghong@bit.edu.cn</t>
+  </si>
+  <si>
+    <t>Beijing Institute of Technology </t>
   </si>
 </sst>
 </file>
@@ -990,12 +1002,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1282,7 +1294,7 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>274</v>
       </c>
       <c r="B3" s="3"/>
@@ -2114,7 +2126,7 @@
       <c r="J26" s="8"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="11" t="s">
         <v>275</v>
       </c>
     </row>
@@ -2445,10 +2457,10 @@
       <c r="J36" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L36" s="11"/>
+      <c r="L36" s="13"/>
     </row>
     <row r="37" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9" t="s">
@@ -2481,10 +2493,10 @@
       <c r="J37" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="L37" s="11"/>
+      <c r="L37" s="13"/>
     </row>
     <row r="38" spans="1:12" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="9" t="s">
@@ -2560,7 +2572,23 @@
         <v>273</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3526,7 +3554,7 @@
   <customSheetViews>
     <customSheetView guid="{8D2DC8AC-2B45-4BEC-859C-DA364D160A20}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:L22" xr:uid="{65081197-C585-45E7-9C6B-2FE2A376895B}"/>
+      <autoFilter ref="A1:L22" xr:uid="{445FF811-972C-4D79-A29D-E818A44263CF}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="92459874"/>
